--- a/data/Omega3/kong2025/kong2025_omega3_depression.xlsx
+++ b/data/Omega3/kong2025/kong2025_omega3_depression.xlsx
@@ -44,7 +44,7 @@
     <t>Year</t>
   </si>
   <si>
-    <t>SMD</t>
+    <t>d</t>
   </si>
   <si>
     <t>lCI</t>
@@ -188,7 +188,7 @@
     <t>notes</t>
   </si>
   <si>
-    <t>n not available, smd used</t>
+    <t>n not available, d used</t>
   </si>
 </sst>
 </file>
